--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
@@ -57,21 +57,21 @@
     <t xml:space="preserve">Castro</t>
   </si>
   <si>
+    <t xml:space="preserve">Calbuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quemchi</t>
   </si>
   <si>
-    <t xml:space="preserve">Calbuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cochamó</t>
   </si>
   <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quinchao</t>
   </si>
   <si>
-    <t xml:space="preserve">Hualaihué</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:20</t>
+    <t xml:space="preserve">2026-09-09 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10209</v>
+        <v>10102</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2019</v>
@@ -701,7 +701,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>10102</v>
+        <v>10209</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2019</v>
@@ -735,7 +735,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10210</v>
+        <v>10403</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2019</v>
@@ -752,7 +752,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10403</v>
+        <v>10210</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:15</t>
+    <t xml:space="preserve">2026-09-17 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
@@ -66,12 +66,12 @@
     <t xml:space="preserve">Cochamó</t>
   </si>
   <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hualaihué</t>
   </si>
   <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:11</t>
+    <t xml:space="preserve">2026-09-23 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -735,7 +735,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10403</v>
+        <v>10210</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2019</v>
@@ -752,7 +752,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10210</v>
+        <v>10403</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:40</t>
+    <t xml:space="preserve">2026-10-02 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2019_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:08</t>
+    <t xml:space="preserve">2026-10-05 11:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
